--- a/backend/backups/category9_health_fitness_wellness_FINAL.xlsx
+++ b/backend/backups/category9_health_fitness_wellness_FINAL.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ALL_SERVICES_FINAL" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,24 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,18 +46,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -74,8 +57,8 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -442,1365 +425,1493 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>service_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>service_name</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>subcategory</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>subcategory</t>
+          <t>name</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>description</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>distinct_features_json</t>
+          <t>highlights</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggested_addons_json</t>
+          <t>included</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>excluded</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>faqs</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>warranty</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>204889e8-705a-5bb2-ade8-da7ce42762ec</t>
+          <t>2ba5e27c-d7ff-5126-ab96-d424a12c30d2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Service Variation 1</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling</t>
+          <t>Core Strength &amp; Calisthenics Trainer</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>950</v>
+        <v>3999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Bodyweight gymnastics, pushup variations, pull-ups, and abdominal core sculpting.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Core Strength &amp; Calisthenics Trainer procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{"text": "Professional mental wellness &amp; counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Mental Wellness &amp; Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Core Strength &amp; Calisthenics Trainer procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.065718+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.065718+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Core Strength &amp; Calisthenics Trainer take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f6667c15-c1ab-551f-a939-407f293cb264</t>
+          <t>37423b94-8ad3-5ffe-9bbc-6ffc64053bef</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Service Variation 2</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling</t>
+          <t>Corporate Desk-Worker Fitness Coach</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1100</v>
+        <v>2999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Posture reset, hip flexor stretch, and quick 30-minute stress-buster workouts.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Corporate Desk-Worker Fitness Coach procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{"text": "Professional mental wellness &amp; counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Mental Wellness &amp; Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Corporate Desk-Worker Fitness Coach procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.070272+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.070272+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Corporate Desk-Worker Fitness Coach take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8779e21f-7909-588c-8d1f-c83a1d0ce9f6</t>
+          <t>086fef9d-c302-517a-b45d-28dd67d5cb5a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Service Variation 3</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling</t>
+          <t>Elderly Mobility &amp; Senior Fitness Trainer</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1250</v>
+        <v>3499</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Gentle low-impact exercises improving balance, leg strength, and joint mobility for senior citizens.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Elderly Mobility &amp; Senior Fitness Trainer procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{"text": "Professional mental wellness &amp; counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Mental Wellness &amp; Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Elderly Mobility &amp; Senior Fitness Trainer procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.073087+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.073087+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Elderly Mobility &amp; Senior Fitness Trainer take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e802b517-8b47-5d0b-b47a-6768c187a156</t>
+          <t>204889e8-705a-5bb2-ade8-da7ce42762ec</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Service Variation 4</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling</t>
+          <t>HIIT &amp; Functional Bodyweight Conditioning</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1400</v>
+        <v>3999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>High-intensity interval training boosting stamina, metabolism, and athletic agility.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional HIIT &amp; Functional Bodyweight Conditioning procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{"text": "Professional mental wellness &amp; counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Mental Wellness &amp; Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete HIIT &amp; Functional Bodyweight Conditioning procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.077518+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.077518+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does HIIT &amp; Functional Bodyweight Conditioning take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5b7013df-172b-5a09-ab5e-6363466c7fb6</t>
+          <t>014dbb7c-f2a5-5154-91f1-c72511dfd9bc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Service Variation 5</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling</t>
+          <t>Personal Home Gym Fitness Trainer (1-on-1)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1550</v>
+        <v>4999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Certified fitness coach bringing resistance bands &amp; dumbbells for weight loss and muscle toning at home.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Personal Home Gym Fitness Trainer (1-on-1) procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{"text": "Professional mental wellness &amp; counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Mental Wellness &amp; Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Personal Home Gym Fitness Trainer (1-on-1) procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.081038+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.081038+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Home Gym Fitness Trainer (1-on-1) take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2ba5e27c-d7ff-5126-ab96-d424a12c30d2</t>
+          <t>325a2da2-5d9e-5689-ae7e-1a64c5934358</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Service Variation 6</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling</t>
+          <t>Post-Pregnancy Weight Loss Coach</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1700</v>
+        <v>4999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Safe diastasis recti recovery, pelvic floor activation, and gradual fat loss exercise.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Post-Pregnancy Weight Loss Coach procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{"text": "Professional mental wellness &amp; counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Mental Wellness &amp; Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Post-Pregnancy Weight Loss Coach procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.084154+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.084154+00:00</t>
+          <t>[{'answer': 'The session typically takes around 45 minutes.', 'question': 'How long does Post-Pregnancy Weight Loss Coach take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>086fef9d-c302-517a-b45d-28dd67d5cb5a</t>
+          <t>2566f951-af68-5072-a8cb-65932557d02c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling Service Variation 1</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling</t>
+          <t>Weight Gain &amp; Muscle Building Coach</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>950</v>
+        <v>4499</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Hypertrophy workout routines, progressive overload tracking, and protein diet guidance.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Weight Gain &amp; Muscle Building Coach procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nutrition &amp; diet counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Nutrition &amp; Diet Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Weight Gain &amp; Muscle Building Coach procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.087794+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.087794+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Weight Gain &amp; Muscle Building Coach take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3f36e9ac-b96d-5a4e-9e23-317f0f199f9a</t>
+          <t>0c2ad276-9094-527f-abf9-fe87d066b22f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling Service Variation 2</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Fitness</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling</t>
+          <t>Zumba &amp; Cardio Dance Workout Trainer</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1100</v>
+        <v>3499</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>High-energy calorie-burning aerobic dance workout session set to upbeat music at home.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Zumba &amp; Cardio Dance Workout Trainer procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nutrition &amp; diet counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Nutrition &amp; Diet Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Zumba &amp; Cardio Dance Workout Trainer procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.091108+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.091108+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Zumba &amp; Cardio Dance Workout Trainer take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6c5c273c-3ccd-5f47-9cda-f39ae93a9945</t>
+          <t>e802b517-8b47-5d0b-b47a-6768c187a156</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling Service Variation 3</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Mental Wellness &amp; Counselling</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling</t>
+          <t>Mental Wellness &amp; Counselling Premium Care Option 19</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1250</v>
+        <v>3899</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nutrition &amp; diet counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Nutrition &amp; Diet Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.095262+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.095262+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>399364d1-7439-53fc-b3a6-36c0c73de25d</t>
+          <t>f6667c15-c1ab-551f-a939-407f293cb264</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling Service Variation 4</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Mental Wellness &amp; Counselling</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling</t>
+          <t>Mental Wellness &amp; Counselling Premium Care Option 21</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1400</v>
+        <v>4099</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 21 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nutrition &amp; diet counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Nutrition &amp; Diet Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 21 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.099287+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.099287+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 21 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2566f951-af68-5072-a8cb-65932557d02c</t>
+          <t>5b7013df-172b-5a09-ab5e-6363466c7fb6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling Service Variation 5</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Mental Wellness &amp; Counselling</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling</t>
+          <t>Mental Wellness &amp; Counselling Premium Care Option 5</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1550</v>
+        <v>2499</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{"text": "Professional nutrition &amp; diet counselling service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Nutrition &amp; Diet Counselling specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.102532+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.102532+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>325a2da2-5d9e-5689-ae7e-1a64c5934358</t>
+          <t>8779e21f-7909-588c-8d1f-c83a1d0ce9f6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Personal Training Service Variation 1</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Mental Wellness &amp; Counselling</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Personal Training</t>
+          <t>Mental Wellness &amp; Counselling Premium Care Option 9</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>950</v>
+        <v>2899</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{"text": "Professional personal training service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Personal Training specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.106599+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.106599+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>b2e904fb-9bf8-577e-b11f-c1497a08ff68</t>
+          <t>6c5c273c-3ccd-5f47-9cda-f39ae93a9945</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Personal Training Service Variation 2</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Nutrition &amp; Diet Counselling</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Personal Training</t>
+          <t>Nutrition &amp; Diet Counselling Premium Care Option 6</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1100</v>
+        <v>2599</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Nutrition &amp; Diet Counselling service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Nutrition &amp; Diet Counselling Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{"text": "Professional personal training service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Personal Training specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Nutrition &amp; Diet Counselling Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.111003+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.111003+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Nutrition &amp; Diet Counselling Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>37423b94-8ad3-5ffe-9bbc-6ffc64053bef</t>
+          <t>a19e0396-6423-5eb5-86cc-79610f36e0a8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Personal Training Service Variation 3</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Personal Training</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Personal Training</t>
+          <t>Personal Training Premium Care Option 12</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1250</v>
+        <v>3199</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Personal Training Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{"text": "Professional personal training service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Personal Training specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Personal Training Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.115656+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.115656+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>a19e0396-6423-5eb5-86cc-79610f36e0a8</t>
+          <t>b2e904fb-9bf8-577e-b11f-c1497a08ff68</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Personal Training Service Variation 4</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Personal Training</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Personal Training</t>
+          <t>Personal Training Premium Care Option 14</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1400</v>
+        <v>3399</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Personal Training Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{"text": "Professional personal training service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Personal Training specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Personal Training Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.120052+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.120052+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f5b2a772-3ace-5c85-a8ad-55437e913f65</t>
+          <t>e7631e11-38b8-5458-bacb-5a6fffcd9bb6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Personal Training Service Variation 5</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Personal Training</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Personal Training</t>
+          <t>Personal Training Premium Care Option 18</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1550</v>
+        <v>3799</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Personal Training Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{"text": "Professional personal training service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Personal Training specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Personal Training Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.123614+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.123614+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>014dbb7c-f2a5-5154-91f1-c72511dfd9bc</t>
+          <t>f5b2a772-3ace-5c85-a8ad-55437e913f65</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Personal Training Service Variation 6</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Personal Training</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Personal Training</t>
+          <t>Personal Training Premium Care Option 20</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1700</v>
+        <v>3999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Personal Training Premium Care Option 20 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{"text": "Professional personal training service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Personal Training specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Personal Training Premium Care Option 20 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.128033+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.128033+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 20 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>e7631e11-38b8-5458-bacb-5a6fffcd9bb6</t>
+          <t>9256c5e4-81d3-5733-8bf3-ffe2fb8d546c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Personal Training Service Variation 7</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Physiotherapy &amp; Rehabilitation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Personal Training</t>
+          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 10</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1850</v>
+        <v>2999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{"text": "Professional personal training service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Personal Training specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.132224+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.132224+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0c2ad276-9094-527f-abf9-fe87d066b22f</t>
+          <t>a1ebe5ec-fd28-597b-a1ba-7d1dfbc3ab88</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Service Variation 1</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Physiotherapy &amp; Rehabilitation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation</t>
+          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 13</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>950</v>
+        <v>3299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{"text": "Professional physiotherapy &amp; rehabilitation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Physiotherapy &amp; Rehabilitation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.135336+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.135336+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9256c5e4-81d3-5733-8bf3-ffe2fb8d546c</t>
+          <t>d24162b7-7c26-515c-81d2-a2dd1b6d6b9c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Service Variation 2</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Physiotherapy &amp; Rehabilitation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation</t>
+          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 15</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1100</v>
+        <v>3499</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{"text": "Professional physiotherapy &amp; rehabilitation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Physiotherapy &amp; Rehabilitation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.138825+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.138825+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>d24162b7-7c26-515c-81d2-a2dd1b6d6b9c</t>
+          <t>e12e5534-f1b9-5152-a626-1c2ce39fc8ce</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Service Variation 3</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Physiotherapy &amp; Rehabilitation</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation</t>
+          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 17</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1250</v>
+        <v>3699</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{"text": "Professional physiotherapy &amp; rehabilitation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Physiotherapy &amp; Rehabilitation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.142929+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.142929+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>e12e5534-f1b9-5152-a626-1c2ce39fc8ce</t>
+          <t>73444069-ba40-5669-bdc3-9772343dcc3f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Service Variation 4</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Physiotherapy &amp; Rehabilitation</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation</t>
+          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 8</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1400</v>
+        <v>2799</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{"text": "Professional physiotherapy &amp; rehabilitation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Physiotherapy &amp; Rehabilitation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.147966+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.147966+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>a1ebe5ec-fd28-597b-a1ba-7d1dfbc3ab88</t>
+          <t>3f36e9ac-b96d-5a4e-9e23-317f0f199f9a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Service Variation 5</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Professional Wellness</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation</t>
+          <t>Professional Wellness Premium Care Option 2</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1550</v>
+        <v>2199</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Professional Wellness service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Professional Wellness Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{"text": "Professional physiotherapy &amp; rehabilitation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Physiotherapy &amp; Rehabilitation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Professional Wellness Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.151770+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.151770+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Professional Wellness Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>73444069-ba40-5669-bdc3-9772343dcc3f</t>
+          <t>399364d1-7439-53fc-b3a6-36c0c73de25d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Service Variation 6</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Sports Coaching</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation</t>
+          <t>Sports Coaching Premium Care Option 1</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1700</v>
+        <v>2099</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Sports Coaching service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Sports Coaching Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{"text": "Professional physiotherapy &amp; rehabilitation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Physiotherapy &amp; Rehabilitation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Sports Coaching Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.155407+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.155407+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Sports Coaching Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ddc2f5a0-2e6f-5cd5-bba3-2b2359f6d683</t>
+          <t>953ecc43-5088-51ab-8b86-d4758c55357f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Service Variation 1</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Yoga &amp; Meditation</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation</t>
+          <t>Yoga &amp; Meditation Premium Care Option 11</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>950</v>
+        <v>3099</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Yoga &amp; Meditation Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{"text": "Professional yoga &amp; meditation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Yoga &amp; Meditation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Yoga &amp; Meditation Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.159032+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.159032+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>402ea739-d08c-56b4-9c11-96ec3b865db2</t>
+          <t>ddc2f5a0-2e6f-5cd5-bba3-2b2359f6d683</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Service Variation 2</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Yoga &amp; Meditation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation</t>
+          <t>Yoga &amp; Meditation Premium Care Option 16</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1100</v>
+        <v>3599</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Yoga &amp; Meditation Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{"text": "Professional yoga &amp; meditation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Yoga &amp; Meditation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Yoga &amp; Meditation Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.165071+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.165071+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1812,95 +1923,105 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Service Variation 3</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Yoga &amp; Meditation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation</t>
+          <t>Yoga &amp; Meditation Premium Care Option 22</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1250</v>
+        <v>4199</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Yoga &amp; Meditation Premium Care Option 22 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{"text": "Professional yoga &amp; meditation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Yoga &amp; Meditation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Yoga &amp; Meditation Premium Care Option 22 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.168139+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.168139+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 22 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6e776f8b-dd09-5612-88ba-c333ebaa6027</t>
+          <t>402ea739-d08c-56b4-9c11-96ec3b865db2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Service Variation 4</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Yoga &amp; Meditation</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation</t>
+          <t>Yoga &amp; Meditation Premium Care Option 3</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1400</v>
+        <v>2299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Yoga &amp; Meditation Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{"text": "Professional yoga &amp; meditation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Yoga &amp; Meditation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Yoga &amp; Meditation Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.171725+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.171725+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
@@ -1912,95 +2033,105 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Service Variation 5</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Yoga &amp; Meditation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation</t>
+          <t>Yoga &amp; Meditation Premium Care Option 4</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1550</v>
+        <v>2399</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Yoga &amp; Meditation Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{"text": "Professional yoga &amp; meditation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Yoga &amp; Meditation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Yoga &amp; Meditation Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.175857+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.175857+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>953ecc43-5088-51ab-8b86-d4758c55357f</t>
+          <t>6e776f8b-dd09-5612-88ba-c333ebaa6027</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Service Variation 6</t>
+          <t>9. Health, Fitness &amp; Wellness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9. Health, Fitness &amp; Wellness</t>
+          <t>Yoga &amp; Meditation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation</t>
+          <t>Yoga &amp; Meditation Premium Care Option 7</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1700</v>
+        <v>2699</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>["Initial health assessment", "Customised session plan", "Post-session feedback", "Digital progress report"]</t>
+          <t>['Professional Yoga &amp; Meditation Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{"text": "Professional yoga &amp; meditation service designed for holistic well-being.", "type": "description"}, {"type": "highlights", "items": ["Certified Yoga &amp; Meditation specialist", "Personalised programme", "Home or studio visits available", "Progress tracking included"]}, {"type": "excluded_scope", "items": ["Gym membership or equipment costs", "Prescription medications"]}, {"type": "process_steps", "steps": [{"title": "Initial Consultation", "description": "Assessing health goals, medical history, and current fitness level", "step_number": 1}, {"title": "Plan Design", "description": "Creating a customised programme tailored to specific needs", "step_number": 2}, {"title": "Session Execution", "description": "Conducting guided sessions with professional supervision", "step_number": 3}, {"title": "Progress Monitoring", "description": "Tracking improvements and adjusting the programme", "step_number": 4}, {"title": "Follow-Up &amp; Review", "description": "Reviewing outcomes and setting next phase goals", "step_number": 5}]}, {"type": "aftercare_precautions", "aftercare": ["Follow post-session cool-down routines", "Adhere to recommended diet and rest"]}, {"type": "tools_materials", "tools": ["Assessment forms", "Exercise equipment (as required)", "Nutritional guides", "Digital tracking tools"], "materials": []}, {"type": "customer_setup", "requirements": ["Wear comfortable clothing", "Ensure adequate space for sessions", "Keep hydrated"]}, {"type": "expected_results", "items": "Improved fitness levels, reduced pain, and enhanced mental well-being."}, {"type": "important_notes", "items": "Please disclose any medical conditions before sessions begin."}, {"type": "warranty", "details": "Free rescheduling for trainer cancellations; first-session satisfaction guarantee.", "has_warranty": true}, {"type": "faqs", "items": [{"answer": "No prior experience is needed; programmes are tailored to all fitness levels.", "question": "Do I need prior experience?"}, {"answer": "Yes, we offer in-home, studio, and online sessions.", "question": "Can sessions happen at my home?"}, {"answer": "Most clients notice improvements within 4-6 weeks with consistent sessions.", "question": "How soon will I see results?"}, {"answer": "Yes, all our health professionals hold valid certifications from recognised bodies.", "question": "Are the professionals certified?"}]}, {"type": "tips", "items": ["Stay consistent — even 3 sessions per week makes a significant difference."]}, {"dos": ["Communicate openly about pain or discomfort during sessions."], "type": "dos_donts", "donts": ["Do not skip prescribed rest days."]}, {"type": "duration", "minutes": 60}]</t>
+          <t>['Complete Yoga &amp; Meditation Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.181311+00:00</t>
+          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-05T15:40:33.181311+00:00</t>
+          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7-day service warranty on workmanship</t>
         </is>
       </c>
     </row>

--- a/backend/backups/category9_health_fitness_wellness_FINAL.xlsx
+++ b/backend/backups/category9_health_fitness_wellness_FINAL.xlsx
@@ -928,7 +928,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>e802b517-8b47-5d0b-b47a-6768c187a156</t>
+          <t>5b7013df-172b-5a09-ab5e-6363466c7fb6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -943,47 +943,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Premium Care Option 19</t>
+          <t>Cognitive Behavioral Therapy (CBT) Session</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3899</v>
+        <v>1499</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
+          <t>Confidential 1-on-1 licensed psychologist session addressing anxiety, stress, and burnout.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 19 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Cognitive Behavioral Therapy (CBT) Session procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 19 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Cognitive Behavioral Therapy (CBT) Session procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 19 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 50 minutes.', 'question': 'How long does Cognitive Behavioral Therapy (CBT) Session take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f6667c15-c1ab-551f-a939-407f293cb264</t>
+          <t>e802b517-8b47-5d0b-b47a-6768c187a156</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -998,47 +998,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Premium Care Option 21</t>
+          <t>Couples Relationship &amp; Pre-Marital Counselling</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4099</v>
+        <v>1999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
+          <t>Empathetic communication conflict resolution and marital alignment counseling.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 21 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Couples Relationship &amp; Pre-Marital Counselling procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 21 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Couples Relationship &amp; Pre-Marital Counselling procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 21 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Couples Relationship &amp; Pre-Marital Counselling take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5b7013df-172b-5a09-ab5e-6363466c7fb6</t>
+          <t>f6667c15-c1ab-551f-a939-407f293cb264</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1053,40 +1053,40 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Premium Care Option 5</t>
+          <t>Mindfulness Meditation &amp; Breathwork Coaching</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2499</v>
+        <v>899</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
+          <t>Guided progressive muscle relaxation and neuro-calming pranayama techniques.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 5 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Mindfulness Meditation &amp; Breathwork Coaching procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 5 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Mindfulness Meditation &amp; Breathwork Coaching procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 5 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Mindfulness Meditation &amp; Breathwork Coaching take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1108,40 +1108,40 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mental Wellness &amp; Counselling Premium Care Option 9</t>
+          <t>Workplace Burnout &amp; Work-Life Balance Therapy</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2899</v>
+        <v>1299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Specialized high-end Mental Wellness &amp; Counselling service tailored to specific client needs with extended guarantee.</t>
+          <t>Therapy counseling managing corporate imposter syndrome, stress, and sleep disorder.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>['Professional Mental Wellness &amp; Counselling Premium Care Option 9 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Workplace Burnout &amp; Work-Life Balance Therapy procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>['Complete Mental Wellness &amp; Counselling Premium Care Option 9 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Workplace Burnout &amp; Work-Life Balance Therapy procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Mental Wellness &amp; Counselling Premium Care Option 9 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Workplace Burnout &amp; Work-Life Balance Therapy take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1163,47 +1163,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Diet Counselling Premium Care Option 6</t>
+          <t>PCOS &amp; Hormonal Balance Nutrition Plan</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2599</v>
+        <v>1299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Specialized high-end Nutrition &amp; Diet Counselling service tailored to specific client needs with extended guarantee.</t>
+          <t>Dietary protocol with low glycemic foods, seed cycling, and insulin management.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>['Professional Nutrition &amp; Diet Counselling Premium Care Option 6 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional PCOS &amp; Hormonal Balance Nutrition Plan procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>['Complete Nutrition &amp; Diet Counselling Premium Care Option 6 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete PCOS &amp; Hormonal Balance Nutrition Plan procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Nutrition &amp; Diet Counselling Premium Care Option 6 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does PCOS &amp; Hormonal Balance Nutrition Plan take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>a19e0396-6423-5eb5-86cc-79610f36e0a8</t>
+          <t>f5b2a772-3ace-5c85-a8ad-55437e913f65</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1218,47 +1218,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Personal Training Premium Care Option 12</t>
+          <t>Body Recomposition &amp; Calorie Deficit Coaching</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3199</v>
+        <v>4499</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
+          <t>Strength training programming paired with weekly digital body fat measurement.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>['Professional Personal Training Premium Care Option 12 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Body Recomposition &amp; Calorie Deficit Coaching procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>['Complete Personal Training Premium Care Option 12 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Body Recomposition &amp; Calorie Deficit Coaching procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 12 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Body Recomposition &amp; Calorie Deficit Coaching take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>b2e904fb-9bf8-577e-b11f-c1497a08ff68</t>
+          <t>a19e0396-6423-5eb5-86cc-79610f36e0a8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1273,47 +1273,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Personal Training Premium Care Option 14</t>
+          <t>Home Kettlebell &amp; Functional Power Trainer</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3399</v>
+        <v>3999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
+          <t>Cardio-endurance kettlebell swing and snatch workouts improving explosive strength.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>['Professional Personal Training Premium Care Option 14 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Home Kettlebell &amp; Functional Power Trainer procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>['Complete Personal Training Premium Care Option 14 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Home Kettlebell &amp; Functional Power Trainer procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 14 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Home Kettlebell &amp; Functional Power Trainer take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>e7631e11-38b8-5458-bacb-5a6fffcd9bb6</t>
+          <t>b2e904fb-9bf8-577e-b11f-c1497a08ff68</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1328,47 +1328,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Personal Training Premium Care Option 18</t>
+          <t>Marathon &amp; Endurance Running Coach</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3799</v>
+        <v>3499</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
+          <t>Gait analysis, cadence pacing drills, and hydration strategies for 10K/21K runners.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>['Professional Personal Training Premium Care Option 18 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Marathon &amp; Endurance Running Coach procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>['Complete Personal Training Premium Care Option 18 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Marathon &amp; Endurance Running Coach procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 18 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Marathon &amp; Endurance Running Coach take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f5b2a772-3ace-5c85-a8ad-55437e913f65</t>
+          <t>e7631e11-38b8-5458-bacb-5a6fffcd9bb6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1383,47 +1383,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Personal Training Premium Care Option 20</t>
+          <t>Weight Loss Boot Camp Session for Couples</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3999</v>
+        <v>4999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Specialized high-end Personal Training service tailored to specific client needs with extended guarantee.</t>
+          <t>High-energy partner workouts combining jump rope, agility ladders, and core circuits.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>['Professional Personal Training Premium Care Option 20 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Weight Loss Boot Camp Session for Couples procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>['Complete Personal Training Premium Care Option 20 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Weight Loss Boot Camp Session for Couples procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Personal Training Premium Care Option 20 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Weight Loss Boot Camp Session for Couples take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9256c5e4-81d3-5733-8bf3-ffe2fb8d546c</t>
+          <t>d24162b7-7c26-515c-81d2-a2dd1b6d6b9c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1438,47 +1438,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 10</t>
+          <t>Cervical Neck Spasm &amp; Migraine Physical Therapy</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2999</v>
+        <v>849</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
+          <t>Suboccipital release massage, cervical traction, and neck posture re-education.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 10 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Cervical Neck Spasm &amp; Migraine Physical Therapy procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 10 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Cervical Neck Spasm &amp; Migraine Physical Therapy procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 10 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Cervical Neck Spasm &amp; Migraine Physical Therapy take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>a1ebe5ec-fd28-597b-a1ba-7d1dfbc3ab88</t>
+          <t>9256c5e4-81d3-5733-8bf3-ffe2fb8d546c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1493,47 +1493,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 13</t>
+          <t>Frozen Shoulder &amp; Rotator Cuff Mobility Rehab</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3299</v>
+        <v>899</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
+          <t>Shoulder pulley exercises, therapeutic ultrasound, and joint mobilization.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 13 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Frozen Shoulder &amp; Rotator Cuff Mobility Rehab procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 13 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Frozen Shoulder &amp; Rotator Cuff Mobility Rehab procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 13 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Frozen Shoulder &amp; Rotator Cuff Mobility Rehab take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>d24162b7-7c26-515c-81d2-a2dd1b6d6b9c</t>
+          <t>a1ebe5ec-fd28-597b-a1ba-7d1dfbc3ab88</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1548,47 +1548,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 15</t>
+          <t>Knee Osteoarthritis Isometric Strengthening</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3499</v>
+        <v>899</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
+          <t>Quadriceps isometric loading, knee taping, and low-impact mobility training.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 15 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Knee Osteoarthritis Isometric Strengthening procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 15 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Knee Osteoarthritis Isometric Strengthening procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 15 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Knee Osteoarthritis Isometric Strengthening take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>e12e5534-f1b9-5152-a626-1c2ce39fc8ce</t>
+          <t>73444069-ba40-5669-bdc3-9772343dcc3f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1603,47 +1603,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 17</t>
+          <t>Lumbar Spondylosis &amp; Sciatica Lower Back Relief</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3699</v>
+        <v>899</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
+          <t>TENS machine stimulation, gentle pelvic tilts, and lumbar traction exercises.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 17 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Lumbar Spondylosis &amp; Sciatica Lower Back Relief procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 17 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Lumbar Spondylosis &amp; Sciatica Lower Back Relief procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 17 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Lumbar Spondylosis &amp; Sciatica Lower Back Relief take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>73444069-ba40-5669-bdc3-9772343dcc3f</t>
+          <t>e12e5534-f1b9-5152-a626-1c2ce39fc8ce</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1658,40 +1658,40 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Physiotherapy &amp; Rehabilitation Premium Care Option 8</t>
+          <t>Post-Stroke Neurological Mobility Home Session</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2799</v>
+        <v>1199</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Specialized high-end Physiotherapy &amp; Rehabilitation service tailored to specific client needs with extended guarantee.</t>
+          <t>Sensory motor repatterning, gait training, and hand grip rehabilitation.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>['Professional Physiotherapy &amp; Rehabilitation Premium Care Option 8 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Post-Stroke Neurological Mobility Home Session procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>['Complete Physiotherapy &amp; Rehabilitation Premium Care Option 8 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Post-Stroke Neurological Mobility Home Session procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Physiotherapy &amp; Rehabilitation Premium Care Option 8 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Post-Stroke Neurological Mobility Home Session take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1713,40 +1713,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Professional Wellness Premium Care Option 2</t>
+          <t>Dry Needling &amp; Myofascial Trigger Point Therapy</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2199</v>
+        <v>999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Specialized high-end Professional Wellness service tailored to specific client needs with extended guarantee.</t>
+          <t>Targeted filament needle insertion into deep muscle knots to release chronic spasms.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>['Professional Professional Wellness Premium Care Option 2 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Dry Needling &amp; Myofascial Trigger Point Therapy procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>['Complete Professional Wellness Premium Care Option 2 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Dry Needling &amp; Myofascial Trigger Point Therapy procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Professional Wellness Premium Care Option 2 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Dry Needling &amp; Myofascial Trigger Point Therapy take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1768,47 +1768,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sports Coaching Premium Care Option 1</t>
+          <t>Tennis / Badminton Footwork &amp; Stroke Coach</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2099</v>
+        <v>2999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Specialized high-end Sports Coaching service tailored to specific client needs with extended guarantee.</t>
+          <t>Court agility ladder drills, backhand mechanics, and smash technique.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>['Professional Sports Coaching Premium Care Option 1 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Tennis / Badminton Footwork &amp; Stroke Coach procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>['Complete Sports Coaching Premium Care Option 1 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Tennis / Badminton Footwork &amp; Stroke Coach procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Sports Coaching Premium Care Option 1 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Tennis / Badminton Footwork &amp; Stroke Coach take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>953ecc43-5088-51ab-8b86-d4758c55357f</t>
+          <t>402ea739-d08c-56b4-9c11-96ec3b865db2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1823,40 +1823,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Premium Care Option 11</t>
+          <t>Ashtanga Primary Series Guided Yoga Flow</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3099</v>
+        <v>3499</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
+          <t>Vinyasa flow synchronizing breath with Surya Namaskar, forward folds, and seated asanas.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>['Professional Yoga &amp; Meditation Premium Care Option 11 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Ashtanga Primary Series Guided Yoga Flow procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>['Complete Yoga &amp; Meditation Premium Care Option 11 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Ashtanga Primary Series Guided Yoga Flow procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 11 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Ashtanga Primary Series Guided Yoga Flow take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1878,40 +1878,40 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Premium Care Option 16</t>
+          <t>Corporate Chair Yoga &amp; Eye Strain Relief</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3599</v>
+        <v>1999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
+          <t>Gentle desk stretches releasing wrist carpal tunnel, neck stiffness, and eye strain.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>['Professional Yoga &amp; Meditation Premium Care Option 16 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Corporate Chair Yoga &amp; Eye Strain Relief procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>['Complete Yoga &amp; Meditation Premium Care Option 16 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Corporate Chair Yoga &amp; Eye Strain Relief procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 16 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Corporate Chair Yoga &amp; Eye Strain Relief take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
@@ -1933,47 +1933,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Premium Care Option 22</t>
+          <t>Kids Yoga &amp; Attention Focus Training</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4199</v>
+        <v>2199</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
+          <t>Playful animal poses, balance games, and breathing exercises boosting concentration.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>['Professional Yoga &amp; Meditation Premium Care Option 22 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Kids Yoga &amp; Attention Focus Training procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>['Complete Yoga &amp; Meditation Premium Care Option 22 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Kids Yoga &amp; Attention Focus Training procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 22 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Kids Yoga &amp; Attention Focus Training take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>402ea739-d08c-56b4-9c11-96ec3b865db2</t>
+          <t>953ecc43-5088-51ab-8b86-d4758c55357f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1988,47 +1988,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Premium Care Option 3</t>
+          <t>Kundalini Chakra Balancing &amp; Mantra Meditation</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2299</v>
+        <v>2799</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
+          <t>Spinal breathing exercises, mudras, and sound vibrational meditation.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>['Professional Yoga &amp; Meditation Premium Care Option 3 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Kundalini Chakra Balancing &amp; Mantra Meditation procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>['Complete Yoga &amp; Meditation Premium Care Option 3 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Kundalini Chakra Balancing &amp; Mantra Meditation procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 3 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 45 minutes.', 'question': 'How long does Kundalini Chakra Balancing &amp; Mantra Meditation take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4f1ccaa5-994d-5bcb-95ce-9923b894b0ce</t>
+          <t>6e776f8b-dd09-5612-88ba-c333ebaa6027</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2043,47 +2043,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Premium Care Option 4</t>
+          <t>Power Yoga Core Sculpt &amp; Sweat Session</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2399</v>
+        <v>3499</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
+          <t>Dynamic fast-paced yoga sequences targeting belly fat, arm balance, and stamina.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>['Professional Yoga &amp; Meditation Premium Care Option 4 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Power Yoga Core Sculpt &amp; Sweat Session procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>['Complete Yoga &amp; Meditation Premium Care Option 4 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Power Yoga Core Sculpt &amp; Sweat Session procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 4 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Power Yoga Core Sculpt &amp; Sweat Session take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6e776f8b-dd09-5612-88ba-c333ebaa6027</t>
+          <t>4f1ccaa5-994d-5bcb-95ce-9923b894b0ce</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2098,40 +2098,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yoga &amp; Meditation Premium Care Option 7</t>
+          <t>Restorative Yin Yoga for Deep Sleep &amp; Flexibility</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2699</v>
+        <v>2999</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Specialized high-end Yoga &amp; Meditation service tailored to specific client needs with extended guarantee.</t>
+          <t>Long-held passive floor poses using bolsters to open fascia and soothe nervous system.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>['Professional Yoga &amp; Meditation Premium Care Option 7 procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
+          <t>['Professional Restorative Yin Yoga for Deep Sleep &amp; Flexibility procedure', 'Certified &amp; background-verified specialists', 'High-grade safety &amp; sanitized tools', '100% satisfaction guarantee', 'Transparent pricing with zero hidden charges']</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>['Complete Yoga &amp; Meditation Premium Care Option 7 procedure', 'Standard tools and supplies included', 'Post-service inspection and cleanup', 'Expert consultation and advice']</t>
+          <t>['Complete Restorative Yin Yoga for Deep Sleep &amp; Flexibility procedure', 'Standard supplies and equipment', 'Post-service cleanup and inspection', 'Expert guidance and aftercare tips']</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>['Structural heavy modifications', 'Spare hardware unless explicitly requested']</t>
+          <t>['Spare parts or structural replacement unless quoted', 'Hazardous materials']</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[{'answer': 'The session typically takes around 60 minutes.', 'question': 'How long does Yoga &amp; Meditation Premium Care Option 7 take?'}, {'answer': 'Yes, strictly industry-approved and sanitized before every appointment.', 'question': 'Are the tools and products safe?'}]</t>
+          <t>[{'answer': 'Typically takes around 60 minutes.', 'question': 'How long does Restorative Yin Yoga for Deep Sleep &amp; Flexibility take?'}, {'answer': 'Yes, exact upfront pricing with zero hidden charges.', 'question': 'Is the pricing transparent?'}]</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7-day service warranty on workmanship</t>
+          <t>7-day service satisfaction warranty</t>
         </is>
       </c>
     </row>
